--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BDEFA8-C4DF-3B4A-8781-1F16021D0F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0242A3B-B3AD-574B-8FD4-89012AA7AB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34820" yWindow="-22020" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1302,6 +1302,9 @@
       <c r="A43" t="s">
         <v>39</v>
       </c>
+      <c r="B43">
+        <v>120</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0242A3B-B3AD-574B-8FD4-89012AA7AB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0305CE-E171-9C4D-8BC6-33A18CAB09B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34820" yWindow="-22020" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,9 @@
   </si>
   <si>
     <t>120 mm at 20%? Sag</t>
+  </si>
+  <si>
+    <t>https://www.wildebikes.com/cdn/shop/files/IMG_1640_5472x.jpg?v=1749103962</t>
   </si>
 </sst>
 </file>
@@ -746,6 +749,11 @@
         <v>99</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0305CE-E171-9C4D-8BC6-33A18CAB09B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6CC649-6564-2C4D-A29D-653337812CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34820" yWindow="-22020" windowWidth="25960" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>https://www.wildebikes.com/cdn/shop/files/IMG_1640_5472x.jpg?v=1749103962</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -703,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1503,6 +1509,14 @@
         <v>83</v>
       </c>
     </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6CC649-6564-2C4D-A29D-653337812CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCE55B8-8C32-944D-B637-2603B1B90998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,24 @@
   </si>
   <si>
     <t>Minneapolis, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1348,172 +1366,202 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50">
-        <v>31.6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B51" s="1"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B56">
+        <v>31.6</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>104</v>
+        <v>48</v>
+      </c>
+      <c r="B58">
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63" s="1">
-        <v>1</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B68">
-        <v>1300</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69">
-        <v>3800</v>
+        <v>59</v>
+      </c>
+      <c r="B69" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>83</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74">
+        <v>1300</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>65</v>
+      </c>
+      <c r="B75">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>67</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>109</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>110</v>
       </c>
     </row>

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCE55B8-8C32-944D-B637-2603B1B90998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A12A862-8348-E24B-A699-516D32E65043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9180" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -1508,7 +1508,9 @@
       <c r="A71" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="1"/>
+      <c r="B71" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -1520,7 +1522,9 @@
       <c r="A73" t="s">
         <v>63</v>
       </c>
-      <c r="B73" s="1"/>
+      <c r="B73" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A12A862-8348-E24B-A699-516D32E65043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9998739-43B8-E94A-9936-2ABB1D7C9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9180" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -341,9 +341,6 @@
     <t>hardtail</t>
   </si>
   <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>threaded 73</t>
   </si>
   <si>
@@ -384,6 +381,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
   </si>
 </sst>
 </file>
@@ -727,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -775,7 +781,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -783,7 +789,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1062,7 +1068,7 @@
         <v>501</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1091,436 +1097,444 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23">
+        <v>120</v>
+      </c>
+      <c r="D23">
+        <v>120</v>
+      </c>
+      <c r="E23">
+        <v>120</v>
+      </c>
+      <c r="F23">
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27">
-        <v>700</v>
-      </c>
-      <c r="D27">
-        <v>700</v>
-      </c>
-      <c r="E27">
-        <v>700</v>
-      </c>
-      <c r="F27">
-        <v>700</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28">
-        <v>2.4</v>
-      </c>
-      <c r="D28">
-        <v>2.4</v>
-      </c>
-      <c r="E28">
-        <v>2.4</v>
-      </c>
-      <c r="F28">
-        <v>2.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="F29">
-        <v>2.6</v>
+        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30">
+        <v>2.4</v>
+      </c>
+      <c r="D30">
+        <v>2.4</v>
+      </c>
+      <c r="E30">
+        <v>2.4</v>
+      </c>
+      <c r="F30">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>2.6</v>
+      </c>
+      <c r="D31">
+        <v>2.6</v>
+      </c>
+      <c r="E31">
+        <v>2.6</v>
+      </c>
+      <c r="F31">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>29</v>
       </c>
-      <c r="C30">
-        <f>C32*2.54</f>
+      <c r="C32">
+        <f>C34*2.54</f>
         <v>157.47999999999999</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:F31" si="1">D32*2.54</f>
+      <c r="D32">
+        <f t="shared" ref="D32:F33" si="1">D34*2.54</f>
         <v>165.1</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="1"/>
         <v>177.8</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="1"/>
         <v>182.88</v>
       </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>30</v>
       </c>
-      <c r="C31">
-        <f>C33*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>167.64000000000001</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <f t="shared" si="1"/>
         <v>180.34</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="1"/>
         <v>193.04</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C32">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C34">
         <v>62</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>65</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>70</v>
       </c>
-      <c r="F32">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33">
-        <v>66</v>
-      </c>
-      <c r="D33">
-        <v>71</v>
-      </c>
-      <c r="E33">
-        <v>73</v>
-      </c>
-      <c r="F33">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="F34">
         <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>100</v>
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35">
+        <v>66</v>
+      </c>
+      <c r="D35">
+        <v>71</v>
+      </c>
+      <c r="E35">
+        <v>73</v>
+      </c>
+      <c r="F35">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40">
-        <v>2.6</v>
+        <v>34</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B42">
-        <v>120</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B44">
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <v>110</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>42</v>
+      </c>
+      <c r="B48">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56">
-        <v>31.6</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>45</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B58">
-        <v>40</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B60">
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>71</v>
@@ -1528,45 +1542,59 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74">
-        <v>1300</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75">
-        <v>3800</v>
+        <v>63</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>66</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>1300</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>67</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>3800</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" t="s">
         <v>109</v>
-      </c>
-      <c r="B78" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Wilde Dark Star 2025.xlsx
+++ b/data/gravel/Wilde Dark Star 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9998739-43B8-E94A-9936-2ABB1D7C9F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{561198C4-FBD7-F64A-B5C0-268AE8CD5224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>a8:f33</t>
+  </si>
+  <si>
+    <t>120-130</t>
   </si>
 </sst>
 </file>
@@ -1336,6 +1339,9 @@
       <c r="A41" t="s">
         <v>35</v>
       </c>
+      <c r="B41">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -1354,8 +1360,8 @@
       <c r="A44" t="s">
         <v>38</v>
       </c>
-      <c r="B44">
-        <v>120</v>
+      <c r="B44" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
